--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -24338,6 +24338,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1043">
+      <c r="A1043" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1043" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C1043" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="D1043" t="n">
+        <v>0.65200001001358</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>0.684000015258789</v>
+      </c>
+      <c r="G1043" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -24361,6 +24361,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1044">
+      <c r="A1044" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1044" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C1044" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="D1044" t="n">
+        <v>0.667999982833862</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>0.667999982833862</v>
+      </c>
+      <c r="G1044" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -24384,6 +24384,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1045">
+      <c r="A1045" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1045" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C1045" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>0.648000001907349</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>0.648000001907349</v>
+      </c>
+      <c r="G1045" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -24407,6 +24407,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1046">
+      <c r="A1046" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1046" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1046" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="G1046" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -24248,22 +24248,22 @@
     </row>
     <row r="1039">
       <c r="A1039" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1039" t="n">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="C1039" t="n">
-        <v>0.670000016689301</v>
+        <v>0.666000008583069</v>
       </c>
       <c r="D1039" t="n">
-        <v>0.648000001907349</v>
+        <v>0.666000008583069</v>
       </c>
       <c r="E1039" t="n">
-        <v>0.670000016689301</v>
+        <v>0.666000008583069</v>
       </c>
       <c r="F1039" t="n">
-        <v>0.653999984264374</v>
+        <v>0.666000008583069</v>
       </c>
       <c r="G1039" t="s">
         <v>7</v>
@@ -24271,19 +24271,19 @@
     </row>
     <row r="1040">
       <c r="A1040" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1040" t="n">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="C1040" t="n">
-        <v>0.660000026226044</v>
+        <v>0.670000016689301</v>
       </c>
       <c r="D1040" t="n">
-        <v>0.653999984264374</v>
+        <v>0.648000001907349</v>
       </c>
       <c r="E1040" t="n">
-        <v>0.660000026226044</v>
+        <v>0.670000016689301</v>
       </c>
       <c r="F1040" t="n">
         <v>0.653999984264374</v>
@@ -24294,22 +24294,22 @@
     </row>
     <row r="1041">
       <c r="A1041" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1041" t="n">
-        <v>32000</v>
+        <v>3500</v>
       </c>
       <c r="C1041" t="n">
-        <v>0.698000013828278</v>
+        <v>0.660000026226044</v>
       </c>
       <c r="D1041" t="n">
-        <v>0.670000016689301</v>
+        <v>0.653999984264374</v>
       </c>
       <c r="E1041" t="n">
-        <v>0.670000016689301</v>
+        <v>0.660000026226044</v>
       </c>
       <c r="F1041" t="n">
-        <v>0.689999997615814</v>
+        <v>0.653999984264374</v>
       </c>
       <c r="G1041" t="s">
         <v>7</v>
@@ -24317,22 +24317,22 @@
     </row>
     <row r="1042">
       <c r="A1042" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1042" t="n">
-        <v>9000</v>
+        <v>32000</v>
       </c>
       <c r="C1042" t="n">
         <v>0.698000013828278</v>
       </c>
       <c r="D1042" t="n">
-        <v>0.674000024795532</v>
+        <v>0.670000016689301</v>
       </c>
       <c r="E1042" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="F1042" t="n">
         <v>0.689999997615814</v>
-      </c>
-      <c r="F1042" t="n">
-        <v>0.698000013828278</v>
       </c>
       <c r="G1042" t="s">
         <v>7</v>
@@ -24340,22 +24340,22 @@
     </row>
     <row r="1043">
       <c r="A1043" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1043" t="n">
-        <v>9500</v>
+        <v>9000</v>
       </c>
       <c r="C1043" t="n">
-        <v>0.689999997615814</v>
+        <v>0.698000013828278</v>
       </c>
       <c r="D1043" t="n">
-        <v>0.65200001001358</v>
+        <v>0.674000024795532</v>
       </c>
       <c r="E1043" t="n">
         <v>0.689999997615814</v>
       </c>
       <c r="F1043" t="n">
-        <v>0.684000015258789</v>
+        <v>0.698000013828278</v>
       </c>
       <c r="G1043" t="s">
         <v>7</v>
@@ -24363,22 +24363,22 @@
     </row>
     <row r="1044">
       <c r="A1044" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1044" t="n">
-        <v>15000</v>
+        <v>9500</v>
       </c>
       <c r="C1044" t="n">
-        <v>0.680000007152557</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="D1044" t="n">
-        <v>0.667999982833862</v>
+        <v>0.65200001001358</v>
       </c>
       <c r="E1044" t="n">
-        <v>0.680000007152557</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="F1044" t="n">
-        <v>0.667999982833862</v>
+        <v>0.684000015258789</v>
       </c>
       <c r="G1044" t="s">
         <v>7</v>
@@ -24386,22 +24386,22 @@
     </row>
     <row r="1045">
       <c r="A1045" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1045" t="n">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="C1045" t="n">
-        <v>0.670000016689301</v>
+        <v>0.680000007152557</v>
       </c>
       <c r="D1045" t="n">
-        <v>0.648000001907349</v>
+        <v>0.667999982833862</v>
       </c>
       <c r="E1045" t="n">
-        <v>0.670000016689301</v>
+        <v>0.680000007152557</v>
       </c>
       <c r="F1045" t="n">
-        <v>0.648000001907349</v>
+        <v>0.667999982833862</v>
       </c>
       <c r="G1045" t="s">
         <v>7</v>
@@ -24409,24 +24409,47 @@
     </row>
     <row r="1046">
       <c r="A1046" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1046" t="n">
-        <v>3000</v>
+        <v>16000</v>
       </c>
       <c r="C1046" t="n">
-        <v>0.656000018119812</v>
+        <v>0.670000016689301</v>
       </c>
       <c r="D1046" t="n">
+        <v>0.648000001907349</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>0.648000001907349</v>
+      </c>
+      <c r="G1046" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1047" t="n">
+        <v>31000</v>
+      </c>
+      <c r="C1047" t="n">
         <v>0.649999976158142</v>
       </c>
-      <c r="E1046" t="n">
+      <c r="D1047" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="E1047" t="n">
         <v>0.649999976158142</v>
       </c>
-      <c r="F1046" t="n">
-        <v>0.656000018119812</v>
-      </c>
-      <c r="G1046" t="s">
+      <c r="F1047" t="n">
+        <v>0.648000001907349</v>
+      </c>
+      <c r="G1047" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -27649,6 +27649,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1050">
+      <c r="A1050" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1050" t="n">
+        <v>29000</v>
+      </c>
+      <c r="C1050" t="n">
+        <v>0.663999974727631</v>
+      </c>
+      <c r="D1050" t="n">
+        <v>0.629999995231628</v>
+      </c>
+      <c r="E1050" t="n">
+        <v>0.663999974727631</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>0.63400000333786</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>0.63400000333786</v>
+      </c>
+      <c r="H1050" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -27675,6 +27675,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1051">
+      <c r="A1051" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1051" t="n">
+        <v>13500</v>
+      </c>
+      <c r="C1051" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>0.632000029087067</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>0.632000029087067</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="H1051" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -27701,6 +27701,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1052">
+      <c r="A1052" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1052" t="n">
+        <v>17500</v>
+      </c>
+      <c r="C1052" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="D1052" t="n">
+        <v>0.632000029087067</v>
+      </c>
+      <c r="E1052" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>0.632000029087067</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>0.632000029087067</v>
+      </c>
+      <c r="H1052" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -27727,6 +27727,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1053">
+      <c r="A1053" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1053" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C1053" t="n">
+        <v>0.653999984264374</v>
+      </c>
+      <c r="D1053" t="n">
+        <v>0.642000019550323</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>0.643999993801117</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="H1053" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -27805,6 +27805,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1056">
+      <c r="A1056" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1056" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C1056" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>0.632000029087067</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="H1056" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -24722,8 +24722,31 @@
       <c r="E1059" t="n">
         <v>0.209000006318092</v>
       </c>
-      <c r="F1059"/>
+      <c r="F1059" t="n">
+        <v>0.156000003218651</v>
+      </c>
       <c r="G1059" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1060" t="n">
+        <v>1244000</v>
+      </c>
+      <c r="C1060" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>0.142000004649162</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>0.145999997854233</v>
+      </c>
+      <c r="F1060"/>
+      <c r="G1060" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -24740,13 +24740,36 @@
         <v>0.17399999499321</v>
       </c>
       <c r="D1060" t="n">
-        <v>0.142000004649162</v>
+        <v>0.140000000596046</v>
       </c>
       <c r="E1060" t="n">
         <v>0.145999997854233</v>
       </c>
-      <c r="F1060"/>
+      <c r="F1060" t="n">
+        <v>0.140000000596046</v>
+      </c>
       <c r="G1060" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1061" t="n">
+        <v>337500</v>
+      </c>
+      <c r="C1061" t="n">
+        <v>0.140000000596046</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>0.120999999344349</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>0.139500007033348</v>
+      </c>
+      <c r="F1061"/>
+      <c r="G1061" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -24768,8 +24768,31 @@
       <c r="E1061" t="n">
         <v>0.139500007033348</v>
       </c>
-      <c r="F1061"/>
+      <c r="F1061" t="n">
+        <v>0.124499998986721</v>
+      </c>
       <c r="G1061" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1062" t="n">
+        <v>425500</v>
+      </c>
+      <c r="C1062" t="n">
+        <v>0.150000005960464</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>0.122500002384186</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>0.123999997973442</v>
+      </c>
+      <c r="F1062"/>
+      <c r="G1062" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -24791,8 +24791,31 @@
       <c r="E1062" t="n">
         <v>0.123999997973442</v>
       </c>
-      <c r="F1062"/>
+      <c r="F1062" t="n">
+        <v>0.150000005960464</v>
+      </c>
       <c r="G1062" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1063" t="n">
+        <v>601000</v>
+      </c>
+      <c r="C1063" t="n">
+        <v>0.156499996781349</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>0.137999996542931</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>0.155000001192093</v>
+      </c>
+      <c r="F1063"/>
+      <c r="G1063" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -24821,6 +24821,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1064">
+      <c r="A1064" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1064" t="n">
+        <v>167000</v>
+      </c>
+      <c r="C1064" t="n">
+        <v>0.148000001907349</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>0.137999996542931</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>0.13850000500679</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>0.138999998569489</v>
+      </c>
+      <c r="G1064" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -28091,6 +28091,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1067">
+      <c r="A1067" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1067" t="n">
+        <v>81000</v>
+      </c>
+      <c r="C1067" t="n">
+        <v>0.136999994516373</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>0.131999999284744</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>0.136999994516373</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>0.134499996900558</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>0.134499996900558</v>
+      </c>
+      <c r="H1067" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -28117,6 +28117,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1068">
+      <c r="A1068" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1068" t="n">
+        <v>72000</v>
+      </c>
+      <c r="C1068" t="n">
+        <v>0.136000007390976</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>0.131999999284744</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>0.135000005364418</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>0.131999999284744</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>0.131999999284744</v>
+      </c>
+      <c r="H1068" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -31379,6 +31379,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1070">
+      <c r="A1070" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1070" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1070" t="n">
+        <v>0.136000007390976</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>0.144999995827675</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>0.13400000333786</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>0.140000000596046</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>0.140000000596046</v>
+      </c>
+      <c r="H1070" t="n">
+        <v>154000</v>
+      </c>
+      <c r="I1070" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -31408,6 +31408,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1071">
+      <c r="A1071" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1071" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1071" t="n">
+        <v>0.142000004649162</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>0.142000004649162</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>0.129999995231628</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>0.13850000500679</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>0.13850000500679</v>
+      </c>
+      <c r="H1071" t="n">
+        <v>157500</v>
+      </c>
+      <c r="I1071" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -31437,6 +31437,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1072">
+      <c r="A1072" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1072" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1072" t="n">
+        <v>0.131500005722046</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>0.143999993801117</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>0.131500005722046</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>0.138999998569489</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>0.138999998569489</v>
+      </c>
+      <c r="H1072" t="n">
+        <v>114000</v>
+      </c>
+      <c r="I1072" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -31466,6 +31466,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1073">
+      <c r="A1073" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1073" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1073" t="n">
+        <v>0.148499995470047</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>0.148499995470047</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>0.13400000333786</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>0.13400000333786</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>0.13400000333786</v>
+      </c>
+      <c r="H1073" t="n">
+        <v>64000</v>
+      </c>
+      <c r="I1073" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -31495,6 +31495,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1074">
+      <c r="A1074" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1074" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1074" t="n">
+        <v>0.134499996900558</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>0.137999996542931</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>0.134499996900558</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>0.137999996542931</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>0.137999996542931</v>
+      </c>
+      <c r="H1074" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I1074" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -31524,6 +31524,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1075">
+      <c r="A1075" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1075" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1075" t="n">
+        <v>0.135000005364418</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>0.135000005364418</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>0.135000005364418</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>0.135000005364418</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>0.135000005364418</v>
+      </c>
+      <c r="H1075" t="n">
+        <v>56000</v>
+      </c>
+      <c r="I1075" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -31553,6 +31553,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1076">
+      <c r="A1076" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1076" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1076" t="n">
+        <v>0.134499996900558</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>0.142000004649162</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>0.134499996900558</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>0.135000005364418</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>0.135000005364418</v>
+      </c>
+      <c r="H1076" t="n">
+        <v>68000</v>
+      </c>
+      <c r="I1076" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENY.MI.xlsx
+++ b/data/ENY.MI.xlsx
@@ -31582,6 +31582,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1077">
+      <c r="A1077" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1077" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1077" t="n">
+        <v>0.136000007390976</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>0.141000002622604</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>0.133000001311302</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>0.13400000333786</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>0.13400000333786</v>
+      </c>
+      <c r="H1077" t="n">
+        <v>115000</v>
+      </c>
+      <c r="I1077" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
